--- a/src/Excelsior.Tests/Headings.MultiLine.verified.xlsx
+++ b/src/Excelsior.Tests/Headings.MultiLine.verified.xlsx
@@ -71,7 +71,7 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>

--- a/src/Excelsior.Tests/Headings.MultiLine.verified.xlsx
+++ b/src/Excelsior.Tests/Headings.MultiLine.verified.xlsx
@@ -68,11 +68,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>

--- a/src/Excelsior.Tests/Headings.MultiLine.verified.xlsx
+++ b/src/Excelsior.Tests/Headings.MultiLine.verified.xlsx
@@ -68,11 +68,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
